--- a/tmap_Result.xlsx
+++ b/tmap_Result.xlsx
@@ -346,309 +346,309 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1">
-        <v>0.8309099082597242</v>
+        <v>0.7443922148907225</v>
       </c>
       <c r="B1">
-        <v>0</v>
+        <v>0.7545670197290786</v>
       </c>
       <c r="C1">
-        <v>0.6262298210414585</v>
+        <v>0.6357378185169256</v>
       </c>
       <c r="D1">
-        <v>0.6678501580345731</v>
+        <v>0.750742153914728</v>
       </c>
       <c r="E1">
-        <v>0.7047751530621958</v>
+        <v>0.7733646996235307</v>
       </c>
       <c r="F1">
-        <v>0.6050081942895249</v>
+        <v>0.6653893837354381</v>
       </c>
       <c r="G1">
-        <v>0</v>
+        <v>0.6680382008740242</v>
       </c>
       <c r="H1">
-        <v>0.7794840197504563</v>
+        <v>0</v>
       </c>
       <c r="I1">
-        <v>0</v>
+        <v>0.5704972871245714</v>
       </c>
       <c r="J1">
-        <v>0.6900407219059724</v>
+        <v>0.7035517129425347</v>
       </c>
       <c r="K1">
-        <v>0.7476185969759299</v>
+        <v>0.5766412663093476</v>
       </c>
       <c r="L1">
-        <v>0.6388652909623235</v>
+        <v>0.6399646988741222</v>
       </c>
       <c r="M1">
-        <v>0.7493597483969173</v>
+        <v>0.6475594207058054</v>
       </c>
       <c r="N1">
-        <v>0.5309811288120461</v>
+        <v>0.6388886238170188</v>
       </c>
       <c r="O1">
-        <v>0</v>
+        <v>0.6537803744754001</v>
       </c>
       <c r="P1">
         <v>0</v>
       </c>
       <c r="Q1">
-        <v>0.6738002451000747</v>
+        <v>0.6882384276350461</v>
       </c>
       <c r="R1">
-        <v>0</v>
+        <v>0.7181737439902139</v>
       </c>
       <c r="S1">
-        <v>0.5190490560834361</v>
+        <v>0</v>
       </c>
       <c r="T1">
-        <v>0.6437864915523357</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:20">
       <c r="A2">
-        <v>0.6972682567715057</v>
+        <v>0.8804724616116857</v>
       </c>
       <c r="B2">
-        <v>0.8528582904140611</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.513545922673622</v>
+        <v>0.6363026825082716</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>0.6050183419160965</v>
       </c>
       <c r="E2">
-        <v>0.5901062855646084</v>
+        <v>0.8046230468327832</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.6032712355810986</v>
       </c>
       <c r="G2">
-        <v>0.7062296761692464</v>
+        <v>0.7372925897435558</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.7644147384849552</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>0.6447144673157871</v>
+        <v>0.6901944360452587</v>
       </c>
       <c r="K2">
-        <v>0.6979216691547806</v>
+        <v>0.5939706483058448</v>
       </c>
       <c r="L2">
-        <v>0.7596824318799095</v>
+        <v>0.730574928352819</v>
       </c>
       <c r="M2">
-        <v>0.8480613809973376</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.5066968134957408</v>
+        <v>0.6027799501046787</v>
       </c>
       <c r="O2">
-        <v>0.9004812281326519</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>0.7152453180785471</v>
+        <v>0.7982807531174173</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.823782931879424</v>
       </c>
       <c r="R2">
-        <v>0.6806400544818014</v>
+        <v>0.8060214119671955</v>
       </c>
       <c r="S2">
-        <v>0.645897118363019</v>
+        <v>0.8118563622790662</v>
       </c>
       <c r="T2">
-        <v>0.7687530854706824</v>
+        <v>0.6528471446552208</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3">
-        <v>0.6984641818924591</v>
+        <v>0</v>
       </c>
       <c r="B3">
-        <v>0.8144077240706066</v>
+        <v>0.7857506143342534</v>
       </c>
       <c r="C3">
-        <v>0.8780089460962691</v>
+        <v>0.7265560286886515</v>
       </c>
       <c r="D3">
-        <v>0.5646935404767729</v>
+        <v>0.6651949654713556</v>
       </c>
       <c r="E3">
-        <v>0.7849207523684388</v>
+        <v>0.9371533591598407</v>
       </c>
       <c r="F3">
-        <v>0.7352338796910717</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>0.5710793789223573</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.8984632513109174</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.5881420370535804</v>
+        <v>0.6901419972504499</v>
       </c>
       <c r="J3">
-        <v>0.7276974708466628</v>
+        <v>0.8171678552826925</v>
       </c>
       <c r="K3">
-        <v>0.7126501525251262</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>0.8813741135094658</v>
+        <v>0.694085203011949</v>
       </c>
       <c r="M3">
-        <v>0.8820463589435016</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9358121552124393</v>
+        <v>0.7225306070187518</v>
       </c>
       <c r="O3">
-        <v>0.6149162207054726</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0.6580894246915463</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>0.7285227434729289</v>
+        <v>0.7382003117024235</v>
       </c>
       <c r="S3">
-        <v>0.5785106792765992</v>
+        <v>0.6935920821869924</v>
       </c>
       <c r="T3">
-        <v>0.532137096838009</v>
+        <v>0.6565337541307901</v>
       </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4">
-        <v>0.6708768622742599</v>
+        <v>0</v>
       </c>
       <c r="B4">
-        <v>0.5863680465744299</v>
+        <v>0.9077081441933278</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>0.8428236214942764</v>
       </c>
       <c r="D4">
-        <v>0.5744707952720614</v>
+        <v>0.6484234275023999</v>
       </c>
       <c r="E4">
-        <v>0.6961892573777829</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>0.6732279753483122</v>
+        <v>0.6840458779900023</v>
       </c>
       <c r="G4">
-        <v>0.7054324795327803</v>
+        <v>0.5734669861780909</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.578635861389361</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.632730038206059</v>
       </c>
       <c r="J4">
-        <v>0.4569190084403671</v>
+        <v>0.6892346292882356</v>
       </c>
       <c r="K4">
-        <v>0.7422883197425429</v>
+        <v>0.8079031547718681</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>0.7264586147204275</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>0.5963816036575669</v>
       </c>
       <c r="N4">
-        <v>0.8652975157729138</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>0.5849576369009239</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>0.6512730995788653</v>
       </c>
       <c r="Q4">
-        <v>0.7154479738954774</v>
+        <v>0.7127378051200041</v>
       </c>
       <c r="R4">
-        <v>0.7762194674098856</v>
+        <v>0.7518131847550333</v>
       </c>
       <c r="S4">
-        <v>0.9098005210786069</v>
+        <v>0.6226849281931515</v>
       </c>
       <c r="T4">
-        <v>0.7044937800555349</v>
+        <v>0.6137374214928482</v>
       </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5">
-        <v>0.5516171153302379</v>
+        <v>0.5701807704270556</v>
       </c>
       <c r="B5">
-        <v>0.5976377820069799</v>
+        <v>0.7755110545918213</v>
       </c>
       <c r="C5">
-        <v>0.787573258567019</v>
+        <v>0.8188298475465282</v>
       </c>
       <c r="D5">
-        <v>0.7466410984941861</v>
+        <v>0.6537340254510134</v>
       </c>
       <c r="E5">
-        <v>0.6432709187697722</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>0.7627812491148881</v>
+        <v>0.7016618629043142</v>
       </c>
       <c r="G5">
-        <v>0.6027514876942651</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>0.7532823643356751</v>
+        <v>0.7408679425022543</v>
       </c>
       <c r="I5">
-        <v>0.8426272322476184</v>
+        <v>0.6574599038545864</v>
       </c>
       <c r="J5">
-        <v>0.5909069469702671</v>
+        <v>0.7502712184106785</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>0.6465059911238696</v>
       </c>
       <c r="L5">
-        <v>0.7374203630313892</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>0.6694366292874148</v>
+        <v>0.5395556653480719</v>
       </c>
       <c r="N5">
-        <v>0.9501309534116212</v>
+        <v>1</v>
       </c>
       <c r="O5">
-        <v>0.8292468297414379</v>
+        <v>0.5798031897522582</v>
       </c>
       <c r="P5">
-        <v>0.9074434618580938</v>
+        <v>0.7151134126512755</v>
       </c>
       <c r="Q5">
-        <v>0.6406256690675811</v>
+        <v>0.78752100064588</v>
       </c>
       <c r="R5">
-        <v>0.5250683409424598</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>0.4973312111718274</v>
+        <v>0.7304076890083185</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -656,64 +656,64 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6">
-        <v>0</v>
+        <v>0.9581666185065052</v>
       </c>
       <c r="B6">
-        <v>0.7883987801609676</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>0.6626756539950555</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>0.6841415940896384</v>
+        <v>0.6443017359721943</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>0.6984822543346787</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>0.7294734382918925</v>
       </c>
       <c r="G6">
-        <v>0.8574498397364451</v>
+        <v>0.6888641915623031</v>
       </c>
       <c r="H6">
-        <v>0.7417603229968392</v>
+        <v>0.6850212481523368</v>
       </c>
       <c r="I6">
-        <v>0.7113523559922583</v>
+        <v>0.6928797294546675</v>
       </c>
       <c r="J6">
-        <v>0.713690270578621</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>0.6721318050893401</v>
+        <v>0.7231212167158101</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>0.6900901178111468</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>0.7845042544906007</v>
       </c>
       <c r="N6">
-        <v>0.5586932955809341</v>
+        <v>0.5716781798361403</v>
       </c>
       <c r="O6">
-        <v>0.6902195656610951</v>
+        <v>0.7535466341269361</v>
       </c>
       <c r="P6">
-        <v>0.7306466614861853</v>
+        <v>0.8593643718252956</v>
       </c>
       <c r="Q6">
-        <v>0.692670699156781</v>
+        <v>0.7427310998704774</v>
       </c>
       <c r="R6">
-        <v>0.7357787141872713</v>
+        <v>0.905176709933617</v>
       </c>
       <c r="S6">
-        <v>0.7486729219717445</v>
+        <v>0.8806584098090338</v>
       </c>
       <c r="T6">
-        <v>0.5780290506104839</v>
+        <v>0.8222271423939267</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -721,492 +721,492 @@
         <v>0</v>
       </c>
       <c r="B7">
-        <v>0.6624198635788293</v>
+        <v>0.718485486753437</v>
       </c>
       <c r="C7">
-        <v>0.7104549309439763</v>
+        <v>0.6622359517768336</v>
       </c>
       <c r="D7">
-        <v>0.7091655112031772</v>
+        <v>0.5772366275238889</v>
       </c>
       <c r="E7">
-        <v>0.6894795523799218</v>
+        <v>0.6802993878456005</v>
       </c>
       <c r="F7">
-        <v>0.5248518750275991</v>
+        <v>0.7416383523242103</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>0.7210659207768751</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>0.5803044799343635</v>
       </c>
       <c r="I7">
-        <v>0.6118200213267092</v>
+        <v>0.7259840921038664</v>
       </c>
       <c r="J7">
-        <v>0.680615937934628</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>0.8063726864935429</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>0.773278965542792</v>
       </c>
       <c r="M7">
-        <v>0.7048416594102814</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>0.7271540276456884</v>
+        <v>0.70482792008634</v>
       </c>
       <c r="O7">
-        <v>0.5055507807901042</v>
+        <v>0.9016452193550465</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>0.7418024941640976</v>
       </c>
       <c r="Q7">
-        <v>0.8138912277055589</v>
+        <v>0.7083954795399019</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>0.8697224022710843</v>
       </c>
       <c r="S7">
-        <v>0.6741528208402023</v>
+        <v>0.5644889559041274</v>
       </c>
       <c r="T7">
-        <v>0.6035780133231288</v>
+        <v>0.6003582689744573</v>
       </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8">
-        <v>0.7218395438897932</v>
+        <v>0.6669524630039803</v>
       </c>
       <c r="B8">
-        <v>0.7780834569061474</v>
+        <v>0.5218501950635455</v>
       </c>
       <c r="C8">
-        <v>0.7942669901348528</v>
+        <v>0.7790456330535723</v>
       </c>
       <c r="D8">
-        <v>0.627944628408394</v>
+        <v>0.6265960218164565</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>0.7059007943780977</v>
+        <v>0.82577891926808</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0.5804756341083745</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>0.5728380612517177</v>
+        <v>0.8945546826563749</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>0.6643470473523952</v>
       </c>
       <c r="K8">
-        <v>0.6148258108352778</v>
+        <v>0.7116810685941937</v>
       </c>
       <c r="L8">
-        <v>0.5844505830559723</v>
+        <v>0.5172638803759366</v>
       </c>
       <c r="M8">
-        <v>0.7537828422136497</v>
+        <v>0.8062630972773258</v>
       </c>
       <c r="N8">
-        <v>0.6666943720167302</v>
+        <v>0.9736902190304082</v>
       </c>
       <c r="O8">
-        <v>0.7467563616641205</v>
+        <v>0.604236270854198</v>
       </c>
       <c r="P8">
-        <v>0.6263162770823117</v>
+        <v>0.6831244905128441</v>
       </c>
       <c r="Q8">
-        <v>0.6967298873830042</v>
+        <v>0.7900252841845693</v>
       </c>
       <c r="R8">
         <v>0</v>
       </c>
       <c r="S8">
-        <v>0.836237067038613</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>0.7323415517529246</v>
+        <v>0.9152288743799827</v>
       </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9">
-        <v>0.7630161535247002</v>
+        <v>0.6582026918174684</v>
       </c>
       <c r="B9">
-        <v>0.673112500144646</v>
+        <v>0.7457457455136633</v>
       </c>
       <c r="C9">
-        <v>0.6890501687651717</v>
+        <v>0.5924950705405452</v>
       </c>
       <c r="D9">
-        <v>0.7385460453277052</v>
+        <v>0.6412882446144064</v>
       </c>
       <c r="E9">
-        <v>0.7131871113854388</v>
+        <v>0.8773390277581056</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>0.6392763304860598</v>
       </c>
       <c r="G9">
-        <v>0.593974138746165</v>
+        <v>0.8617952878620717</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>0.8951482331772401</v>
       </c>
       <c r="I9">
-        <v>0.6668979510672813</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>0.5932942073400735</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>0.5811761740611096</v>
+        <v>0.566298612370686</v>
       </c>
       <c r="L9">
-        <v>0.7444089564554778</v>
+        <v>0.7009056659135624</v>
       </c>
       <c r="M9">
-        <v>0.7810747973932441</v>
+        <v>0.5852812407393231</v>
       </c>
       <c r="N9">
-        <v>0.8142307191560215</v>
+        <v>0.8666434865135241</v>
       </c>
       <c r="O9">
-        <v>0.7429594222002703</v>
+        <v>0.7843185102318996</v>
       </c>
       <c r="P9">
-        <v>0.5856641807686258</v>
+        <v>0.6378596801495372</v>
       </c>
       <c r="Q9">
-        <v>0.5443692568047613</v>
+        <v>0.7468316077557664</v>
       </c>
       <c r="R9">
-        <v>0.6871092446680082</v>
+        <v>0.7078114246586289</v>
       </c>
       <c r="S9">
-        <v>0.7169536029046911</v>
+        <v>0.8888232088259045</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>0.7231740581962963</v>
       </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10">
-        <v>0</v>
+        <v>0.6966980589734378</v>
       </c>
       <c r="B10">
-        <v>0.6544717956578668</v>
+        <v>0.6896071568394991</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0.6484729438947711</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>0.5970041781933428</v>
+        <v>0.6650973125779842</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>0.7331103027923771</v>
       </c>
       <c r="G10">
-        <v>0.8497381862131301</v>
+        <v>0.588040464338271</v>
       </c>
       <c r="H10">
-        <v>0.5230961953537661</v>
+        <v>0.5867656468413996</v>
       </c>
       <c r="I10">
-        <v>0.8668516955032174</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>0.6322079593230364</v>
+        <v>0.5184576890652927</v>
       </c>
       <c r="K10">
-        <v>0.524812561128626</v>
+        <v>0.7868993599417555</v>
       </c>
       <c r="L10">
-        <v>0.5179857750004874</v>
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>0.6190120610820928</v>
+        <v>0.5690076094914231</v>
       </c>
       <c r="N10">
         <v>0</v>
       </c>
       <c r="O10">
-        <v>0.7386134075119859</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>0.6466380986916653</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>0.6079974688555682</v>
+        <v>0.7601534338017667</v>
       </c>
       <c r="R10">
-        <v>0.5336669365816876</v>
+        <v>0.7246192378530822</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
       <c r="T10">
-        <v>0.5962774328497819</v>
+        <v>0.7910570368694694</v>
       </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11">
-        <v>0.6512444975835423</v>
+        <v>0.6799876871126421</v>
       </c>
       <c r="B11">
-        <v>0.5521566462328669</v>
+        <v>0.6066481213412442</v>
       </c>
       <c r="C11">
-        <v>0.5839256138875315</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>0.7021783449421877</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>0.6483130448120118</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>0.9413403664664404</v>
+        <v>0.7755409892151713</v>
       </c>
       <c r="H11">
-        <v>0.9237899614533961</v>
+        <v>0.5117990238651668</v>
       </c>
       <c r="I11">
-        <v>0.6379783424268766</v>
+        <v>0.7598195249792774</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>0.8234787010382172</v>
       </c>
       <c r="K11">
-        <v>0.6850185478609973</v>
+        <v>0.6559298953196508</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>0.6392310403267147</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>0.8273291654864576</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>0.5713030931911031</v>
       </c>
       <c r="O11">
-        <v>0.6722653505099604</v>
+        <v>0.6500788573263889</v>
       </c>
       <c r="P11">
-        <v>0.6331815554066342</v>
+        <v>0.5892713888167048</v>
       </c>
       <c r="Q11">
-        <v>0.8808036405284818</v>
+        <v>0.6871218968034244</v>
       </c>
       <c r="R11">
-        <v>0.5997093537941637</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>0.7168428711859475</v>
+        <v>0.8757613077949506</v>
       </c>
       <c r="T11">
-        <v>0.4745462818297584</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12">
-        <v>0</v>
+        <v>0.8019989672239968</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>0.8912480096954302</v>
       </c>
       <c r="C12">
-        <v>0.7849761467129877</v>
+        <v>0.7625511398310022</v>
       </c>
       <c r="D12">
-        <v>0.6003987956370536</v>
+        <v>0.6987071926445565</v>
       </c>
       <c r="E12">
-        <v>0.6339942465446522</v>
+        <v>0.5905027029589617</v>
       </c>
       <c r="F12">
-        <v>0.9309351428788465</v>
+        <v>0.6410020670948905</v>
       </c>
       <c r="G12">
-        <v>0.7521309758554742</v>
+        <v>0.7335246235446795</v>
       </c>
       <c r="H12">
-        <v>0.7838275226767513</v>
+        <v>0.7594144243220089</v>
       </c>
       <c r="I12">
-        <v>0.5829801293829115</v>
+        <v>0.6243898359595077</v>
       </c>
       <c r="J12">
-        <v>0.6576562379089096</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>0.7550090119893736</v>
+        <v>0.657822454634403</v>
       </c>
       <c r="L12">
-        <v>0.7495502347427967</v>
+        <v>0.591051895751961</v>
       </c>
       <c r="M12">
-        <v>0.5423416255254531</v>
+        <v>0.7163999536553509</v>
       </c>
       <c r="N12">
-        <v>0.6594996326960378</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>0.8129059751620136</v>
+        <v>0.7134793390802691</v>
       </c>
       <c r="P12">
-        <v>0.544638469161303</v>
+        <v>0.6479901574642206</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>0.6546092737172177</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>0.5950643321001141</v>
       </c>
       <c r="S12">
-        <v>0.5531885177173907</v>
+        <v>0.8707779069087336</v>
       </c>
       <c r="T12">
-        <v>0.6444581127951795</v>
+        <v>0.777004539494676</v>
       </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13">
-        <v>0.7860961791588608</v>
+        <v>0.8102014861835539</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>0.8977764758226712</v>
       </c>
       <c r="C13">
-        <v>0.7818126980815211</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>0.8754178519413761</v>
+        <v>0.6027406133144142</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>0.5937670976132779</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>0.4626461593628964</v>
       </c>
       <c r="G13">
-        <v>0.5389065103976804</v>
+        <v>0.6346167150003587</v>
       </c>
       <c r="H13">
-        <v>0.570063652934688</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>0.550596106354559</v>
+        <v>0.6278699854499274</v>
       </c>
       <c r="J13">
-        <v>0.8409827788905857</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>0.8136132345660136</v>
+        <v>0</v>
       </c>
       <c r="L13">
-        <v>0.5331908563243593</v>
+        <v>0.7563002045973013</v>
       </c>
       <c r="M13">
-        <v>0.7236485561216183</v>
+        <v>0.7989572921322606</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>0.8358996754482835</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>0.5482381868761945</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>0.5838650357465428</v>
       </c>
       <c r="R13">
-        <v>0.7426541345178772</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>0.7300287879680893</v>
+        <v>0.7297819316029421</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>0.6084623529653387</v>
       </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14">
-        <v>0.7648930125344046</v>
+        <v>0.5774942813950777</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>0.8318944149261507</v>
       </c>
       <c r="C14">
-        <v>0.4792296041215179</v>
+        <v>0.6344364295670508</v>
       </c>
       <c r="D14">
-        <v>0.6288528745282305</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>0.7955248271345237</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>0.6204103434991518</v>
+        <v>0.7078459800007667</v>
       </c>
       <c r="G14">
-        <v>0.5829126723419583</v>
+        <v>0.630000994071962</v>
       </c>
       <c r="H14">
-        <v>0.7018854958055423</v>
+        <v>0.6288222288435469</v>
       </c>
       <c r="I14">
-        <v>0.7218665294366318</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>0.9040409337051487</v>
+        <v>0.78958728245883</v>
       </c>
       <c r="K14">
-        <v>0.9097063581919681</v>
+        <v>0</v>
       </c>
       <c r="L14">
-        <v>0.8276701166409315</v>
+        <v>0.6558742084215563</v>
       </c>
       <c r="M14">
-        <v>0.7224809293262345</v>
+        <v>0.795943896358119</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>0.6859503237669253</v>
       </c>
       <c r="O14">
-        <v>0.7715141337397726</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>0.6977072912020574</v>
+        <v>0.7581817829882707</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>0.7063535187663187</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>0.8015925279270248</v>
       </c>
       <c r="S14">
-        <v>0.5945945438415722</v>
+        <v>0.7551557318543578</v>
       </c>
       <c r="T14">
         <v>0</v>
@@ -1214,326 +1214,326 @@
     </row>
     <row r="15" spans="1:20">
       <c r="A15">
-        <v>0</v>
+        <v>0.9077978554126436</v>
       </c>
       <c r="B15">
-        <v>0.6100773062751856</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>0.9107199283692073</v>
+        <v>0.8628815102350303</v>
       </c>
       <c r="D15">
-        <v>0.4942180824498048</v>
+        <v>0.8492626369311621</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>0.716074116406572</v>
       </c>
       <c r="F15">
-        <v>0.6679583255759337</v>
+        <v>0.7371632116080381</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>0.8307472804622086</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0.7457961926764419</v>
+        <v>0.8099952832519984</v>
       </c>
       <c r="J15">
-        <v>0.7248289825243585</v>
+        <v>0.8359662069689042</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0.5684279514451616</v>
+        <v>0</v>
       </c>
       <c r="M15">
-        <v>0.7014221771889428</v>
+        <v>0.6441122710732843</v>
       </c>
       <c r="N15">
-        <v>0.7391379784239368</v>
+        <v>0.6813961844852074</v>
       </c>
       <c r="O15">
-        <v>0.670161327910324</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>0.7051616537016169</v>
+        <v>0.6715652807745964</v>
       </c>
       <c r="Q15">
-        <v>0.6269332139336762</v>
+        <v>0.5332191468792837</v>
       </c>
       <c r="R15">
         <v>0</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>0.8110203912614197</v>
       </c>
       <c r="T15">
-        <v>0.5820089744710188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16">
-        <v>0.7016652291627535</v>
+        <v>0.6503019137922003</v>
       </c>
       <c r="B16">
-        <v>0.7508304691012099</v>
+        <v>0.7698366326125089</v>
       </c>
       <c r="C16">
-        <v>0.7975398729963047</v>
+        <v>0.6422310346812808</v>
       </c>
       <c r="D16">
-        <v>0.6535319456189732</v>
+        <v>0.762136145231473</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0.6399929487398809</v>
       </c>
       <c r="F16">
-        <v>0.8063584189079689</v>
+        <v>0.7700507050621906</v>
       </c>
       <c r="G16">
-        <v>0.6019859247145378</v>
+        <v>0.7296910351314672</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>0.6033199644145966</v>
       </c>
       <c r="I16">
-        <v>0.740415742478065</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>0.4697658967558932</v>
+        <v>0.7086642797133949</v>
       </c>
       <c r="K16">
-        <v>0.5391635275412313</v>
+        <v>0</v>
       </c>
       <c r="L16">
-        <v>0.5692990835108135</v>
+        <v>0.7236185950175673</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>0.7019463620949982</v>
       </c>
       <c r="N16">
-        <v>0.6832079230755805</v>
+        <v>0.6939971091229463</v>
       </c>
       <c r="O16">
-        <v>0.6504666773748444</v>
+        <v>0.6141446930945743</v>
       </c>
       <c r="P16">
-        <v>0.7757521056941412</v>
+        <v>0.6982979346033468</v>
       </c>
       <c r="Q16">
-        <v>0.7334619844084873</v>
+        <v>0.6209585976384061</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>0.9192721131626886</v>
       </c>
       <c r="S16">
-        <v>0.673833018986203</v>
+        <v>0.6760088907405493</v>
       </c>
       <c r="T16">
-        <v>0.7216718901545925</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:20">
       <c r="A17">
-        <v>0</v>
+        <v>0.6721659912384357</v>
       </c>
       <c r="B17">
-        <v>0.9267290777883704</v>
+        <v>0.645179300292344</v>
       </c>
       <c r="C17">
-        <v>0.6122986923280316</v>
+        <v>0.5143831530469695</v>
       </c>
       <c r="D17">
-        <v>0.6360457961493349</v>
+        <v>0.5444089265026272</v>
       </c>
       <c r="E17">
-        <v>0.5048134672255938</v>
+        <v>0.8733578726473178</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>0.8637445523815269</v>
       </c>
       <c r="G17">
-        <v>0.68635157645981</v>
+        <v>0.6942968505925308</v>
       </c>
       <c r="H17">
-        <v>0.7509595312392353</v>
+        <v>0.6705218584582456</v>
       </c>
       <c r="I17">
-        <v>0.7259054414628043</v>
+        <v>0.7091861789711701</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17">
-        <v>0.6053755372150481</v>
+        <v>0.7661789175799408</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>0.7543497606730201</v>
       </c>
       <c r="M17">
-        <v>0.8443025630073363</v>
+        <v>0.6374554051842288</v>
       </c>
       <c r="N17">
-        <v>0.6781094199475072</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>0.7388505047598911</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>0.782926851682072</v>
+        <v>0.6924681517466521</v>
       </c>
       <c r="Q17">
-        <v>0.6595112219945872</v>
+        <v>0.730224030340855</v>
       </c>
       <c r="R17">
-        <v>0.6616784493444626</v>
+        <v>0.8692380456546608</v>
       </c>
       <c r="S17">
-        <v>0.6437336586236271</v>
+        <v>0.797494516809123</v>
       </c>
       <c r="T17">
-        <v>0.6731615662907587</v>
+        <v>0.5608776290414622</v>
       </c>
     </row>
     <row r="18" spans="1:20">
       <c r="A18">
-        <v>0.5620651087187019</v>
+        <v>0.9072619928167385</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>0.5412953884051548</v>
       </c>
       <c r="D18">
-        <v>0.8588747614460903</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>0.7482326922648984</v>
+        <v>0</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>0.6234346025531408</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>0.9064844273488956</v>
+        <v>0.5982800100341494</v>
       </c>
       <c r="I18">
-        <v>0.6927388483607644</v>
+        <v>0.9395379751556554</v>
       </c>
       <c r="J18">
-        <v>0.7293952619064412</v>
+        <v>0.6227802453872872</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>0.7341582693829792</v>
       </c>
       <c r="L18">
-        <v>0.6222094679104199</v>
+        <v>0.7635019413654845</v>
       </c>
       <c r="M18">
-        <v>0.6444710235289201</v>
+        <v>0</v>
       </c>
       <c r="N18">
-        <v>0.6504154469339883</v>
+        <v>0.6336531407752658</v>
       </c>
       <c r="O18">
-        <v>0.6590209381206255</v>
+        <v>0.5294182217673246</v>
       </c>
       <c r="P18">
-        <v>0.7223623710625199</v>
+        <v>0.753187062516088</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>0.6422320357732072</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>0.6776048066823392</v>
       </c>
       <c r="S18">
-        <v>0.6391639147133036</v>
+        <v>0.6603820968031335</v>
       </c>
       <c r="T18">
-        <v>0.6254548813207315</v>
+        <v>0.6226798810635166</v>
       </c>
     </row>
     <row r="19" spans="1:20">
       <c r="A19">
-        <v>0</v>
+        <v>0.5566337612459913</v>
       </c>
       <c r="B19">
-        <v>0.6990695951316455</v>
+        <v>0.9021925806122454</v>
       </c>
       <c r="C19">
-        <v>0.6207987633068253</v>
+        <v>0.5119316966719836</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>0.8995153241510755</v>
       </c>
       <c r="E19">
-        <v>0.6714885859520167</v>
+        <v>0.6522507561295712</v>
       </c>
       <c r="F19">
-        <v>0.7174168263310357</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>0.8570051220910381</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>0.7521939643751298</v>
+        <v>0.7167827236617424</v>
       </c>
       <c r="I19">
-        <v>0.563601119321555</v>
+        <v>0.672368506304072</v>
       </c>
       <c r="J19">
-        <v>0.7556436559349645</v>
+        <v>0.8689822379138085</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>0.6170971581788764</v>
       </c>
       <c r="L19">
-        <v>0.6596464003297005</v>
+        <v>0</v>
       </c>
       <c r="M19">
-        <v>0.7060387814189275</v>
+        <v>0.8837974860464429</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>0.7878548119701785</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>0.6384427373036546</v>
+        <v>0.8058093012440076</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>0.7112326536325118</v>
       </c>
       <c r="R19">
         <v>0</v>
       </c>
       <c r="S19">
-        <v>0.5939210904773563</v>
+        <v>0.5963135868927332</v>
       </c>
       <c r="T19">
-        <v>0.5415719441373592</v>
+        <v>0.8154472791873841</v>
       </c>
     </row>
     <row r="20" spans="1:20">
       <c r="A20">
-        <v>0.6023709248979824</v>
+        <v>0.5181861408843706</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>0.6218044560100345</v>
       </c>
       <c r="C20">
-        <v>0.7593544289191849</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>0.7684082808987146</v>
+        <v>0</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1542,46 +1542,46 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>0.7145261566216122</v>
+        <v>0.6204607876838647</v>
       </c>
       <c r="H20">
-        <v>0.6624117625586171</v>
+        <v>0.7896488471210468</v>
       </c>
       <c r="I20">
-        <v>0.755939057636738</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>0.7960195082172014</v>
       </c>
       <c r="K20">
-        <v>0.6345348332504422</v>
+        <v>0</v>
       </c>
       <c r="L20">
-        <v>0.5230752443362031</v>
+        <v>0.659194722135947</v>
       </c>
       <c r="M20">
-        <v>0.5243046356526037</v>
+        <v>0</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>0.8561052482590408</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>0.5739964200469273</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>0.7843398820137529</v>
       </c>
       <c r="Q20">
-        <v>0.8383938171692803</v>
+        <v>0.6973606422433941</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>0.620431992888371</v>
       </c>
       <c r="S20">
-        <v>0.5995473196777102</v>
+        <v>0.5541781773294795</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>0.9861718943032739</v>
       </c>
     </row>
   </sheetData>
@@ -1599,7 +1599,7 @@
         <v>-1</v>
       </c>
       <c r="B1">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C1">
         <v>-1</v>
@@ -1614,13 +1614,13 @@
         <v>-1</v>
       </c>
       <c r="G1">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1">
         <v>1</v>
@@ -1638,22 +1638,22 @@
         <v>1</v>
       </c>
       <c r="O1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1">
         <v>0</v>
       </c>
       <c r="Q1">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R1">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T1">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -1661,19 +1661,19 @@
         <v>-1</v>
       </c>
       <c r="B2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E2">
         <v>-1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -1682,7 +1682,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -1691,22 +1691,22 @@
         <v>1</v>
       </c>
       <c r="L2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R2">
         <v>-1</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -1750,87 +1750,87 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3">
         <v>1</v>
       </c>
       <c r="O3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3">
         <v>-1</v>
       </c>
       <c r="S3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="T3">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -1844,28 +1844,28 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -1874,10 +1874,10 @@
         <v>1</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1889,16 +1889,16 @@
         <v>-1</v>
       </c>
       <c r="P5">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -1906,43 +1906,43 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N6">
         <v>1</v>
@@ -1954,10 +1954,10 @@
         <v>1</v>
       </c>
       <c r="Q6">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="S6">
         <v>1</v>
@@ -1974,58 +1974,58 @@
         <v>1</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O7">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7">
         <v>1</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7">
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -2033,31 +2033,31 @@
         <v>1</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -2066,16 +2066,16 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="Q8">
         <v>1</v>
@@ -2084,7 +2084,7 @@
         <v>0</v>
       </c>
       <c r="S8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8">
         <v>1</v>
@@ -2092,40 +2092,40 @@
     </row>
     <row r="9" spans="1:20">
       <c r="A9">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K9">
         <v>1</v>
       </c>
       <c r="L9">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="M9">
         <v>1</v>
@@ -2137,10 +2137,10 @@
         <v>1</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R9">
         <v>1</v>
@@ -2149,45 +2149,45 @@
         <v>1</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10">
         <v>-1</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J10">
         <v>-1</v>
       </c>
       <c r="K10">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M10">
         <v>1</v>
@@ -2196,13 +2196,13 @@
         <v>0</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R10">
         <v>1</v>
@@ -2219,72 +2219,72 @@
         <v>-1</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G11">
         <v>-1</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I11">
         <v>1</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O11">
         <v>1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -2293,7 +2293,7 @@
         <v>-1</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G12">
         <v>-1</v>
@@ -2305,7 +2305,7 @@
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K12">
         <v>-1</v>
@@ -2317,87 +2317,87 @@
         <v>-1</v>
       </c>
       <c r="N12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S12">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="T12">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G13">
         <v>-1</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L13">
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13">
         <v>1</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -2405,19 +2405,19 @@
         <v>-1</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G14">
         <v>-1</v>
@@ -2426,37 +2426,37 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14">
         <v>1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L14">
         <v>1</v>
       </c>
       <c r="M14">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="T14">
         <v>0</v>
@@ -2464,25 +2464,25 @@
     </row>
     <row r="15" spans="1:20">
       <c r="A15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15">
         <v>-1</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -2497,31 +2497,31 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M15">
         <v>-1</v>
       </c>
       <c r="N15">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P15">
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R15">
         <v>0</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -2532,37 +2532,37 @@
         <v>1</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G16">
         <v>1</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L16">
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -2577,60 +2577,60 @@
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16">
         <v>1</v>
       </c>
       <c r="T16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:20">
       <c r="A17">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H17">
         <v>1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M17">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2642,33 +2642,33 @@
         <v>1</v>
       </c>
       <c r="S17">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="T17">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="18" spans="1:20">
       <c r="A18">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -2680,16 +2680,16 @@
         <v>1</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L18">
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -2698,13 +2698,13 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S18">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="T18">
         <v>1</v>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="19" spans="1:20">
       <c r="A19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -2721,16 +2721,16 @@
         <v>1</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E19">
         <v>-1</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H19">
         <v>-1</v>
@@ -2742,16 +2742,16 @@
         <v>1</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -2760,7 +2760,7 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -2769,7 +2769,7 @@
         <v>1</v>
       </c>
       <c r="T19">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="20" spans="1:20">
@@ -2777,13 +2777,13 @@
         <v>1</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2792,46 +2792,46 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H20">
         <v>-1</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L20">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="M20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S20">
         <v>1</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
